--- a/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_44.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_44.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2922289.537670172</v>
+        <v>2915422.544721516</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.4107162900211</v>
+        <v>286.4107162900382</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286.4107162900211</v>
+        <v>286.4107162900382</v>
       </c>
     </row>
     <row r="11">
@@ -672,10 +672,10 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>8.009658703527407</v>
+        <v>36.71585008894188</v>
       </c>
       <c r="I2" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -742,16 +742,16 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>300.9629961541974</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>308.4311513056531</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>21.95645751172319</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -857,7 +857,7 @@
         <v>287.4478973282775</v>
       </c>
       <c r="Q4" t="n">
-        <v>325.839266425598</v>
+        <v>324.2480957795422</v>
       </c>
       <c r="R4" t="n">
         <v>326.6021279811511</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>94.84816780232291</v>
+        <v>123.5543591877376</v>
       </c>
       <c r="T5" t="n">
         <v>186.6755817285639</v>
@@ -957,7 +957,7 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>220.9880248460822</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
         <v>111.3174326828064</v>
@@ -973,13 +973,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1021,16 +1021,16 @@
         <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
-        <v>66.5639999646113</v>
+        <v>211.1281943176416</v>
       </c>
       <c r="T6" t="n">
-        <v>154.0457902577147</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
         <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
-        <v>14.51066719152016</v>
+        <v>385</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>21.95645751172409</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
         <v>120.6316114025499</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573350953</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>32.46356367243068</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102.4466513351298</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1219,13 +1219,13 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>199.8180013219744</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>385</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
-        <v>385</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>21.95645751172319</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573350953</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H11" t="n">
         <v>58.00965870352741</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>144.8481678023229</v>
@@ -1444,13 +1444,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34.55655664632661</v>
+        <v>230.1079332804206</v>
       </c>
       <c r="C12" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>239.5984974349628</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>197.2737972923793</v>
@@ -1620,7 +1620,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H14" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>299.2212965486107</v>
       </c>
       <c r="V14" t="n">
-        <v>283.8164155522384</v>
+        <v>279.8510241668239</v>
       </c>
       <c r="W14" t="n">
         <v>288.3734759809475</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>121.4947832967418</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C15" t="n">
         <v>11.09991244551929</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1744,10 +1744,10 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>69.86273944538755</v>
+        <v>132.54050197083</v>
       </c>
       <c r="Y15" t="n">
         <v>49.39139276613435</v>
@@ -1851,7 +1851,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F17" t="n">
-        <v>58.85502009342638</v>
+        <v>54.88962870801186</v>
       </c>
       <c r="G17" t="n">
         <v>53.75737228701621</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S17" t="n">
         <v>144.8481678023229</v>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>86.93822665041522</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H18" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>80.50967533902144</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2088,7 +2088,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F20" t="n">
-        <v>58.85502009342638</v>
+        <v>54.88962870801186</v>
       </c>
       <c r="G20" t="n">
         <v>53.75737228701621</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S20" t="n">
         <v>144.8481678023229</v>
@@ -2161,13 +2161,13 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>73.04152018756569</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>62.67776252544251</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>197.2737972923793</v>
@@ -2218,7 +2218,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>432.3731429098285</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X21" t="n">
         <v>69.86273944538755</v>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>131.9993129555745</v>
+        <v>135.964704340989</v>
       </c>
       <c r="C23" t="n">
         <v>99.47457824299391</v>
@@ -2376,7 +2376,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W23" t="n">
-        <v>292.3388673663621</v>
+        <v>288.3734759809475</v>
       </c>
       <c r="X23" t="n">
         <v>242.2818334606677</v>
@@ -2395,7 +2395,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2410,10 +2410,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>195.551376634094</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2458,7 +2458,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X24" t="n">
-        <v>132.5405019708301</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y24" t="n">
         <v>49.39139276613435</v>
@@ -2565,7 +2565,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H26" t="n">
         <v>58.00965870352741</v>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T26" t="n">
         <v>236.6755817285639</v>
@@ -2632,13 +2632,13 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>62.67776252544243</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2677,10 +2677,10 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>197.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S27" t="n">
-        <v>466.5639999646113</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T27" t="n">
         <v>55.35776521751382</v>
@@ -2805,7 +2805,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H29" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>236.6755817285639</v>
       </c>
       <c r="U29" t="n">
-        <v>303.1866879340253</v>
+        <v>299.2212965486107</v>
       </c>
       <c r="V29" t="n">
         <v>279.8510241668239</v>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C30" t="n">
         <v>11.09991244551929</v>
@@ -2881,10 +2881,10 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>62.67776252544251</v>
       </c>
       <c r="H30" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>80.50967533902136</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>197.2737972923793</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T32" t="n">
         <v>236.6755817285639</v>
@@ -3087,7 +3087,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W32" t="n">
-        <v>288.3734759809475</v>
+        <v>292.3388673663621</v>
       </c>
       <c r="X32" t="n">
         <v>242.2818334606677</v>
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>80.50967533902147</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -3121,10 +3121,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>332.1680871864211</v>
+        <v>195.551376634094</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T35" t="n">
         <v>236.6755817285639</v>
@@ -3343,13 +3343,13 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>84.14143263308497</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>73.04152018756569</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S38" t="n">
         <v>144.8481678023229</v>
@@ -3561,7 +3561,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>292.3388673663621</v>
+        <v>288.3734759809475</v>
       </c>
       <c r="X38" t="n">
         <v>242.2818334606677</v>
@@ -3592,10 +3592,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S39" t="n">
         <v>116.5639999646113</v>
@@ -3637,7 +3637,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V39" t="n">
-        <v>127.1884297169626</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W39" t="n">
         <v>82.37314290982852</v>
@@ -3756,7 +3756,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>144.8481678023229</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>34.55655664632661</v>
+        <v>97.23431917176904</v>
       </c>
       <c r="C42" t="n">
         <v>11.09991244551929</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S42" t="n">
         <v>116.5639999646113</v>
@@ -3877,10 +3877,10 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>145.050905435271</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X42" t="n">
-        <v>419.8627394453875</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
         <v>49.39139276613435</v>
@@ -3981,7 +3981,7 @@
         <v>60.33915573984979</v>
       </c>
       <c r="E44" t="n">
-        <v>54.36328960686865</v>
+        <v>58.32868099228319</v>
       </c>
       <c r="F44" t="n">
         <v>54.88962870801186</v>
@@ -4038,7 +4038,7 @@
         <v>288.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>246.2472248460823</v>
+        <v>242.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>161.3174326828064</v>
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4096,10 +4096,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>80.50967533902136</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S45" t="n">
         <v>116.5639999646113</v>
@@ -4120,7 +4120,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>49.39139276613435</v>
+        <v>112.0691552915768</v>
       </c>
     </row>
     <row r="46">
@@ -4315,31 +4315,31 @@
         <v>67.88671726155745</v>
       </c>
       <c r="H2" t="n">
-        <v>59.79615291456007</v>
+        <v>30.8</v>
       </c>
       <c r="I2" t="n">
         <v>30.8</v>
       </c>
       <c r="J2" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="M2" t="n">
         <v>411.95</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>411.95</v>
       </c>
-      <c r="L2" t="n">
-        <v>411.95</v>
-      </c>
-      <c r="M2" t="n">
-        <v>793.1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>793.1</v>
-      </c>
       <c r="O2" t="n">
-        <v>1158.85</v>
+        <v>793.0999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>1158.85</v>
+        <v>1174.25</v>
       </c>
       <c r="Q2" t="n">
         <v>1540</v>
@@ -4385,13 +4385,13 @@
         <v>897.189519579215</v>
       </c>
       <c r="E3" t="n">
-        <v>897.189519579215</v>
+        <v>593.1864931608338</v>
       </c>
       <c r="F3" t="n">
-        <v>897.189519579215</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="G3" t="n">
-        <v>585.6429020987573</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="H3" t="n">
         <v>250.1195817084329</v>
@@ -4455,25 +4455,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>381.9465518290261</v>
+        <v>229.621392885946</v>
       </c>
       <c r="C4" t="n">
-        <v>507.9485576474619</v>
+        <v>229.621392885946</v>
       </c>
       <c r="D4" t="n">
-        <v>621.267701772462</v>
+        <v>282.3059186249661</v>
       </c>
       <c r="E4" t="n">
-        <v>621.267701772462</v>
+        <v>400.1348228363792</v>
       </c>
       <c r="F4" t="n">
-        <v>745.6286743643975</v>
+        <v>524.4957954283146</v>
       </c>
       <c r="G4" t="n">
-        <v>899.0352402512827</v>
+        <v>677.9023613151999</v>
       </c>
       <c r="H4" t="n">
-        <v>1068.55182541068</v>
+        <v>847.4189464745974</v>
       </c>
       <c r="I4" t="n">
         <v>1068.55182541068</v>
@@ -4485,19 +4485,19 @@
         <v>1540</v>
       </c>
       <c r="L4" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012344</v>
       </c>
       <c r="M4" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N4" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O4" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P4" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q4" t="n">
         <v>360.7011393749001</v>
@@ -4509,22 +4509,22 @@
         <v>30.8</v>
       </c>
       <c r="T4" t="n">
-        <v>71.71585826404794</v>
+        <v>30.8</v>
       </c>
       <c r="U4" t="n">
-        <v>71.71585826404794</v>
+        <v>30.8</v>
       </c>
       <c r="V4" t="n">
-        <v>270.5372511499939</v>
+        <v>229.621392885946</v>
       </c>
       <c r="W4" t="n">
-        <v>270.5372511499939</v>
+        <v>229.621392885946</v>
       </c>
       <c r="X4" t="n">
-        <v>270.5372511499939</v>
+        <v>229.621392885946</v>
       </c>
       <c r="Y4" t="n">
-        <v>381.9465518290261</v>
+        <v>229.621392885946</v>
       </c>
     </row>
     <row r="5">
@@ -4558,25 +4558,25 @@
         <v>30.8</v>
       </c>
       <c r="J5" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="M5" t="n">
         <v>411.95</v>
       </c>
-      <c r="K5" t="n">
+      <c r="N5" t="n">
         <v>411.95</v>
       </c>
-      <c r="L5" t="n">
-        <v>411.95</v>
-      </c>
-      <c r="M5" t="n">
-        <v>793.1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1174.25</v>
-      </c>
       <c r="O5" t="n">
-        <v>1540</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>1540</v>
+        <v>1158.85</v>
       </c>
       <c r="Q5" t="n">
         <v>1540</v>
@@ -4585,19 +4585,19 @@
         <v>1540</v>
       </c>
       <c r="S5" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T5" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U5" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V5" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W5" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X5" t="n">
         <v>307.7196251784331</v>
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>746.9995952961838</v>
+        <v>376.9334315372855</v>
       </c>
       <c r="C6" t="n">
-        <v>382.2522089875785</v>
+        <v>376.9334315372855</v>
       </c>
       <c r="D6" t="n">
-        <v>30.8</v>
+        <v>376.9334315372855</v>
       </c>
       <c r="E6" t="n">
         <v>30.8</v>
@@ -4664,25 +4664,25 @@
         <v>1037.471008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>970.2346453614745</v>
+        <v>824.2102066210398</v>
       </c>
       <c r="T6" t="n">
-        <v>814.6328370203485</v>
+        <v>818.798322562945</v>
       </c>
       <c r="U6" t="n">
-        <v>814.4203524140992</v>
+        <v>818.5858379566957</v>
       </c>
       <c r="V6" t="n">
-        <v>799.7631128267051</v>
+        <v>429.6969490678068</v>
       </c>
       <c r="W6" t="n">
-        <v>767.0629684733429</v>
+        <v>396.9968047144446</v>
       </c>
       <c r="X6" t="n">
-        <v>746.9995952961838</v>
+        <v>376.9334315372855</v>
       </c>
       <c r="Y6" t="n">
-        <v>746.9995952961838</v>
+        <v>376.9334315372855</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>915.0975767666613</v>
+        <v>1058.488973253216</v>
       </c>
       <c r="C7" t="n">
-        <v>1041.099582585097</v>
+        <v>1184.490979071652</v>
       </c>
       <c r="D7" t="n">
-        <v>1041.099582585097</v>
+        <v>1297.810123196652</v>
       </c>
       <c r="E7" t="n">
-        <v>1041.099582585097</v>
+        <v>1415.639027408065</v>
       </c>
       <c r="F7" t="n">
-        <v>1165.460555177033</v>
+        <v>1540</v>
       </c>
       <c r="G7" t="n">
-        <v>1318.867121063918</v>
+        <v>1540</v>
       </c>
       <c r="H7" t="n">
-        <v>1318.867121063918</v>
+        <v>1540</v>
       </c>
       <c r="I7" t="n">
-        <v>1540.000000000001</v>
+        <v>1540</v>
       </c>
       <c r="J7" t="n">
-        <v>1540.000000000001</v>
+        <v>1540</v>
       </c>
       <c r="K7" t="n">
-        <v>1540.000000000001</v>
+        <v>1540</v>
       </c>
       <c r="L7" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012344</v>
       </c>
       <c r="M7" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N7" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O7" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P7" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q7" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R7" t="n">
         <v>30.8</v>
       </c>
       <c r="S7" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T7" t="n">
-        <v>68.05025509417312</v>
+        <v>67.02804009978786</v>
       </c>
       <c r="U7" t="n">
-        <v>314.6014477324597</v>
+        <v>313.5792327380745</v>
       </c>
       <c r="V7" t="n">
-        <v>513.4228406184056</v>
+        <v>512.4006256240204</v>
       </c>
       <c r="W7" t="n">
-        <v>685.313758878083</v>
+        <v>684.2915438836978</v>
       </c>
       <c r="X7" t="n">
-        <v>836.3445499022765</v>
+        <v>835.3223349078913</v>
       </c>
       <c r="Y7" t="n">
-        <v>915.0975767666613</v>
+        <v>946.7316355869236</v>
       </c>
     </row>
     <row r="8">
@@ -4786,31 +4786,31 @@
         <v>71.68204280399807</v>
       </c>
       <c r="G8" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H8" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I8" t="n">
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
-        <v>411.9500000000011</v>
+        <v>411.95</v>
       </c>
       <c r="K8" t="n">
-        <v>411.9500000000011</v>
+        <v>411.95</v>
       </c>
       <c r="L8" t="n">
-        <v>411.9500000000011</v>
+        <v>411.95</v>
       </c>
       <c r="M8" t="n">
-        <v>411.9500000000011</v>
+        <v>793.1</v>
       </c>
       <c r="N8" t="n">
-        <v>793.1000000000024</v>
+        <v>1174.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1174.250000000004</v>
+        <v>1540</v>
       </c>
       <c r="P8" t="n">
         <v>1540</v>
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
       <c r="C9" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
       <c r="D9" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
       <c r="E9" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
       <c r="F9" t="n">
-        <v>30.8</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="G9" t="n">
-        <v>30.8</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="H9" t="n">
         <v>30.8</v>
@@ -4907,19 +4907,19 @@
         <v>964.8227613033797</v>
       </c>
       <c r="U9" t="n">
-        <v>575.9338724144908</v>
+        <v>964.6102766971304</v>
       </c>
       <c r="V9" t="n">
-        <v>187.0449835256019</v>
+        <v>949.9530371097363</v>
       </c>
       <c r="W9" t="n">
-        <v>154.3448391722397</v>
+        <v>917.2528927563742</v>
       </c>
       <c r="X9" t="n">
-        <v>134.2814659950806</v>
+        <v>897.189519579215</v>
       </c>
       <c r="Y9" t="n">
-        <v>134.2814659950806</v>
+        <v>897.189519579215</v>
       </c>
     </row>
     <row r="10">
@@ -4929,22 +4929,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>934.3125068406187</v>
+        <v>514.4329432708497</v>
       </c>
       <c r="C10" t="n">
-        <v>934.3125068406187</v>
+        <v>640.4349490892855</v>
       </c>
       <c r="D10" t="n">
-        <v>1047.631650965619</v>
+        <v>753.7540932142856</v>
       </c>
       <c r="E10" t="n">
-        <v>1165.460555177032</v>
+        <v>871.5829974256986</v>
       </c>
       <c r="F10" t="n">
-        <v>1165.460555177032</v>
+        <v>995.9439700176341</v>
       </c>
       <c r="G10" t="n">
-        <v>1318.867121063917</v>
+        <v>1149.350535904519</v>
       </c>
       <c r="H10" t="n">
         <v>1318.867121063917</v>
@@ -4959,46 +4959,46 @@
         <v>1540</v>
       </c>
       <c r="L10" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012344</v>
       </c>
       <c r="M10" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N10" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O10" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P10" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q10" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R10" t="n">
         <v>30.8</v>
       </c>
       <c r="S10" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T10" t="n">
-        <v>256.125934252978</v>
+        <v>30.8</v>
       </c>
       <c r="U10" t="n">
-        <v>502.6771268912646</v>
+        <v>30.8</v>
       </c>
       <c r="V10" t="n">
-        <v>701.4985197772105</v>
+        <v>30.8</v>
       </c>
       <c r="W10" t="n">
-        <v>873.3894380368879</v>
+        <v>140.2355139013318</v>
       </c>
       <c r="X10" t="n">
-        <v>873.3894380368879</v>
+        <v>291.2663049255253</v>
       </c>
       <c r="Y10" t="n">
-        <v>873.3894380368879</v>
+        <v>402.6756056045576</v>
       </c>
     </row>
     <row r="11">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C11" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D11" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E11" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F11" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G11" t="n">
         <v>103.3156148520479</v>
@@ -5032,22 +5032,22 @@
         <v>44.72</v>
       </c>
       <c r="J11" t="n">
-        <v>436.0291130376557</v>
+        <v>137.1709049473327</v>
       </c>
       <c r="K11" t="n">
-        <v>436.0291130376557</v>
+        <v>137.1709049473327</v>
       </c>
       <c r="L11" t="n">
-        <v>436.0291130376557</v>
+        <v>137.1709049473327</v>
       </c>
       <c r="M11" t="n">
-        <v>946.8779417665908</v>
+        <v>137.1709049473327</v>
       </c>
       <c r="N11" t="n">
-        <v>1500.287941766591</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="O11" t="n">
-        <v>1797.400904947332</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P11" t="n">
         <v>1797.400904947332</v>
@@ -5056,28 +5056,28 @@
         <v>2236</v>
       </c>
       <c r="R11" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S11" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T11" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U11" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V11" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W11" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X11" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y11" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="12">
@@ -5087,25 +5087,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>297.950717050992</v>
+        <v>275.2516144816847</v>
       </c>
       <c r="C12" t="n">
-        <v>286.7386842777402</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="D12" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="E12" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="F12" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="G12" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="H12" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I12" t="n">
         <v>44.72</v>
@@ -5132,31 +5132,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>1025.324879873102</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>826.0584179616072</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S12" t="n">
-        <v>708.3170038559392</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T12" t="n">
-        <v>652.400069292794</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U12" t="n">
-        <v>601.6825341814942</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V12" t="n">
-        <v>536.5202440890496</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W12" t="n">
-        <v>453.3150492306369</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X12" t="n">
-        <v>382.7466255484273</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y12" t="n">
-        <v>332.8563298250593</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="13">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C14" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D14" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E14" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G14" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H14" t="n">
         <v>44.72</v>
@@ -5269,25 +5269,25 @@
         <v>44.72</v>
       </c>
       <c r="J14" t="n">
-        <v>44.72</v>
+        <v>64.92117127106526</v>
       </c>
       <c r="K14" t="n">
-        <v>598.13</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="L14" t="n">
-        <v>1151.54</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="M14" t="n">
-        <v>1151.54</v>
+        <v>1129.18</v>
       </c>
       <c r="N14" t="n">
-        <v>1704.95</v>
+        <v>1682.59</v>
       </c>
       <c r="O14" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P14" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q14" t="n">
         <v>2236</v>
@@ -5305,16 +5305,16 @@
         <v>1548.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X14" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y14" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="15">
@@ -5324,19 +5324,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.9618669904511</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C15" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="D15" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="E15" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="F15" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="G15" t="n">
         <v>44.72</v>
@@ -5387,13 +5387,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W15" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X15" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y15" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="16">
@@ -5403,16 +5403,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C16" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D16" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E16" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F16" t="n">
         <v>1153.55685638681</v>
@@ -5457,22 +5457,22 @@
         <v>44.72</v>
       </c>
       <c r="T16" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U16" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V16" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W16" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X16" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y16" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="17">
@@ -5482,16 +5482,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C17" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D17" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E17" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F17" t="n">
         <v>157.615990899539</v>
@@ -5506,52 +5506,52 @@
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>44.72</v>
+        <v>64.92117127106526</v>
       </c>
       <c r="K17" t="n">
-        <v>598.13</v>
+        <v>64.92117127106526</v>
       </c>
       <c r="L17" t="n">
-        <v>1151.54</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="M17" t="n">
-        <v>1151.54</v>
+        <v>1129.18</v>
       </c>
       <c r="N17" t="n">
-        <v>1704.95</v>
+        <v>1682.59</v>
       </c>
       <c r="O17" t="n">
-        <v>1704.95</v>
+        <v>2236</v>
       </c>
       <c r="P17" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q17" t="n">
         <v>2236</v>
       </c>
       <c r="R17" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S17" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T17" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U17" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V17" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W17" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X17" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y17" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="18">
@@ -5573,13 +5573,13 @@
         <v>461.5662247731743</v>
       </c>
       <c r="F18" t="n">
-        <v>461.5662247731743</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G18" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="H18" t="n">
-        <v>126.0429043828499</v>
+        <v>44.72</v>
       </c>
       <c r="I18" t="n">
         <v>44.72</v>
@@ -5719,16 +5719,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C20" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D20" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E20" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F20" t="n">
         <v>157.615990899539</v>
@@ -5746,49 +5746,49 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M20" t="n">
-        <v>1243.990904947333</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="N20" t="n">
-        <v>1797.400904947332</v>
+        <v>1129.18</v>
       </c>
       <c r="O20" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="P20" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
       </c>
       <c r="R20" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S20" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T20" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U20" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V20" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W20" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X20" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y20" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="21">
@@ -5798,16 +5798,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C21" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D21" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="E21" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F21" t="n">
         <v>44.72</v>
@@ -5843,31 +5843,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>1136.841549130715</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R21" t="n">
-        <v>937.5750872192206</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S21" t="n">
-        <v>819.8336731135525</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T21" t="n">
-        <v>763.9167385504073</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U21" t="n">
-        <v>713.1992034391076</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V21" t="n">
-        <v>648.036913346663</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W21" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X21" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y21" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="22">
@@ -5940,7 +5940,7 @@
         <v>529.6682646830375</v>
       </c>
       <c r="W22" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X22" t="n">
         <v>745.8791912947012</v>
@@ -5980,25 +5980,25 @@
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>598.13</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M23" t="n">
-        <v>1108.978828728935</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N23" t="n">
-        <v>1662.388828728935</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O23" t="n">
-        <v>1682.59</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P23" t="n">
-        <v>2236</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="Q23" t="n">
         <v>2236</v>
@@ -6019,13 +6019,13 @@
         <v>1265.70093914513</v>
       </c>
       <c r="W23" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X23" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y23" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="24">
@@ -6035,25 +6035,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>409.4673863086053</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C24" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D24" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E24" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F24" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G24" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="H24" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I24" t="n">
         <v>44.72</v>
@@ -6101,10 +6101,10 @@
         <v>628.142589726071</v>
       </c>
       <c r="X24" t="n">
-        <v>494.2632948060406</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y24" t="n">
-        <v>444.3729990826726</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="25">
@@ -6114,7 +6114,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C25" t="n">
         <v>946.5478354584615</v>
@@ -6168,22 +6168,22 @@
         <v>44.72</v>
       </c>
       <c r="T25" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U25" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V25" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W25" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X25" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y25" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="26">
@@ -6193,19 +6193,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C26" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D26" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E26" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F26" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G26" t="n">
         <v>103.3156148520479</v>
@@ -6217,25 +6217,25 @@
         <v>44.72</v>
       </c>
       <c r="J26" t="n">
-        <v>137.1709049473328</v>
+        <v>64.92117127106515</v>
       </c>
       <c r="K26" t="n">
-        <v>137.1709049473328</v>
+        <v>618.3311712710652</v>
       </c>
       <c r="L26" t="n">
-        <v>690.5809049473327</v>
+        <v>1171.741171271065</v>
       </c>
       <c r="M26" t="n">
-        <v>690.5809049473327</v>
+        <v>1682.59</v>
       </c>
       <c r="N26" t="n">
-        <v>690.5809049473327</v>
+        <v>2236</v>
       </c>
       <c r="O26" t="n">
-        <v>1243.990904947333</v>
+        <v>2236</v>
       </c>
       <c r="P26" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q26" t="n">
         <v>2236</v>
@@ -6244,25 +6244,25 @@
         <v>2236</v>
       </c>
       <c r="S26" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T26" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U26" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V26" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W26" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X26" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y26" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="27">
@@ -6272,13 +6272,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>119.2429040110725</v>
+        <v>409.4673863086053</v>
       </c>
       <c r="C27" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="D27" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="E27" t="n">
         <v>44.72</v>
@@ -6320,28 +6320,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R27" t="n">
-        <v>1000.885958457041</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S27" t="n">
-        <v>529.6091908160197</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T27" t="n">
-        <v>473.6922562528744</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U27" t="n">
-        <v>422.9747211415747</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V27" t="n">
-        <v>357.8124310491301</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W27" t="n">
-        <v>274.6072361907174</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X27" t="n">
-        <v>204.0388125085078</v>
+        <v>494.2632948060406</v>
       </c>
       <c r="Y27" t="n">
-        <v>154.1485167851397</v>
+        <v>444.3729990826726</v>
       </c>
     </row>
     <row r="28">
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C29" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D29" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E29" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F29" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G29" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H29" t="n">
         <v>44.72</v>
@@ -6454,25 +6454,25 @@
         <v>44.72</v>
       </c>
       <c r="J29" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>44.72</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L29" t="n">
-        <v>179.7320762183977</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M29" t="n">
-        <v>690.5809049473327</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N29" t="n">
-        <v>690.5809049473327</v>
+        <v>1682.59</v>
       </c>
       <c r="O29" t="n">
-        <v>1243.990904947333</v>
+        <v>1682.59</v>
       </c>
       <c r="P29" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q29" t="n">
         <v>2236</v>
@@ -6487,19 +6487,19 @@
         <v>1850.622475221327</v>
       </c>
       <c r="U29" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V29" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W29" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X29" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y29" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="30">
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>391.4553531635761</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C30" t="n">
-        <v>380.2433203903244</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D30" t="n">
-        <v>380.2433203903244</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="E30" t="n">
-        <v>380.2433203903244</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="F30" t="n">
-        <v>380.2433203903244</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="G30" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H30" t="n">
         <v>44.72</v>
@@ -6554,31 +6554,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>1118.829515985686</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R30" t="n">
-        <v>919.5630540741914</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S30" t="n">
-        <v>801.8216399685234</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T30" t="n">
-        <v>745.9047054053782</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U30" t="n">
-        <v>695.1871702940784</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V30" t="n">
-        <v>630.0248802016338</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W30" t="n">
-        <v>546.8196853432211</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X30" t="n">
-        <v>476.2512616610114</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y30" t="n">
-        <v>426.3609659376434</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="31">
@@ -6700,13 +6700,13 @@
         <v>436.0291130376557</v>
       </c>
       <c r="M32" t="n">
-        <v>690.5809049473327</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N32" t="n">
-        <v>1243.990904947333</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O32" t="n">
-        <v>1243.990904947333</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="P32" t="n">
         <v>1797.400904947332</v>
@@ -6718,16 +6718,16 @@
         <v>2236</v>
       </c>
       <c r="S32" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T32" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U32" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V32" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W32" t="n">
         <v>970.4091539265823</v>
@@ -6755,16 +6755,16 @@
         <v>461.5662247731743</v>
       </c>
       <c r="E33" t="n">
-        <v>380.2433203903244</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F33" t="n">
-        <v>380.2433203903244</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G33" t="n">
-        <v>380.2433203903244</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="H33" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I33" t="n">
         <v>44.72</v>
@@ -6825,16 +6825,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C34" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D34" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E34" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F34" t="n">
         <v>1153.55685638681</v>
@@ -6879,22 +6879,22 @@
         <v>44.72</v>
       </c>
       <c r="T34" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U34" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V34" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W34" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X34" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y34" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="35">
@@ -6934,25 +6934,25 @@
         <v>436.0291130376557</v>
       </c>
       <c r="L35" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M35" t="n">
-        <v>989.4391130376558</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N35" t="n">
-        <v>1542.849113037656</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O35" t="n">
-        <v>1682.59</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P35" t="n">
-        <v>2236</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S35" t="n">
         <v>2085.68327354774</v>
@@ -6986,10 +6986,10 @@
         <v>472.7782575464261</v>
       </c>
       <c r="C36" t="n">
-        <v>387.7869114524009</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D36" t="n">
-        <v>387.7869114524009</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E36" t="n">
         <v>387.7869114524009</v>
@@ -7062,16 +7062,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C37" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D37" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E37" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F37" t="n">
         <v>1153.55685638681</v>
@@ -7116,22 +7116,22 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U37" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V37" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W37" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X37" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y37" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="38">
@@ -7171,37 +7171,37 @@
         <v>44.72</v>
       </c>
       <c r="L38" t="n">
-        <v>575.7700000000003</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M38" t="n">
-        <v>575.7700000000003</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N38" t="n">
-        <v>1129.18</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O38" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P38" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q38" t="n">
         <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S38" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T38" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U38" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V38" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W38" t="n">
         <v>970.4091539265823</v>
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C39" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D39" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E39" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F39" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G39" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H39" t="n">
         <v>44.72</v>
@@ -7268,28 +7268,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S39" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T39" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U39" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V39" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W39" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X39" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y39" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="40">
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C40" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D40" t="n">
         <v>1010.366979583462</v>
@@ -7353,22 +7353,22 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U40" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V40" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W40" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="41">
@@ -7378,43 +7378,43 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C41" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D41" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E41" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F41" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G41" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H41" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I41" t="n">
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="K41" t="n">
-        <v>989.4391130376558</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="L41" t="n">
-        <v>989.4391130376558</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M41" t="n">
-        <v>1500.287941766591</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N41" t="n">
-        <v>1797.400904947332</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O41" t="n">
         <v>1797.400904947332</v>
@@ -7426,28 +7426,28 @@
         <v>2236</v>
       </c>
       <c r="R41" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S41" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T41" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U41" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V41" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W41" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X41" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y41" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="42">
@@ -7505,28 +7505,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S42" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T42" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U42" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V42" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W42" t="n">
-        <v>564.8317184882503</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X42" t="n">
-        <v>140.7279412706871</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y42" t="n">
-        <v>90.8376455473191</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="43">
@@ -7615,13 +7615,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C44" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D44" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E44" t="n">
         <v>213.0600603015712</v>
@@ -7645,19 +7645,19 @@
         <v>598.13</v>
       </c>
       <c r="L44" t="n">
-        <v>1151.54</v>
+        <v>598.13</v>
       </c>
       <c r="M44" t="n">
-        <v>1151.54</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="N44" t="n">
-        <v>1704.95</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="O44" t="n">
-        <v>2236</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P44" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
@@ -7681,10 +7681,10 @@
         <v>974.4145997704354</v>
       </c>
       <c r="X44" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y44" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>391.4553531635761</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="D45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="E45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="F45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="G45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H45" t="n">
         <v>44.72</v>
@@ -7739,31 +7739,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q45" t="n">
-        <v>1118.829515985686</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>919.5630540741914</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S45" t="n">
-        <v>801.8216399685234</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T45" t="n">
-        <v>745.9047054053782</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U45" t="n">
-        <v>695.1871702940784</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V45" t="n">
-        <v>630.0248802016338</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W45" t="n">
-        <v>546.8196853432211</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X45" t="n">
-        <v>476.2512616610114</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y45" t="n">
-        <v>426.3609659376434</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="46">
@@ -7773,31 +7773,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C46" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D46" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E46" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F46" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G46" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H46" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I46" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J46" t="n">
-        <v>1868.407409693835</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K46" t="n">
         <v>1921.561060958496</v>
@@ -7827,22 +7827,22 @@
         <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U46" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V46" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W46" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X46" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y46" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
   </sheetData>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>420.0430062450903</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7979,13 +7979,13 @@
         <v>477.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>439.6923140185368</v>
+        <v>455.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2870600406814136</v>
+        <v>385.2870600406814</v>
       </c>
       <c r="Q2" t="n">
-        <v>557.8226843274854</v>
+        <v>542.2671287719298</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,7 +8201,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>420.0430062450903</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -8213,16 +8213,16 @@
         <v>929.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>862.2489580698352</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O5" t="n">
         <v>439.6923140185369</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2870600406814136</v>
+        <v>385.2870600406814</v>
       </c>
       <c r="Q5" t="n">
-        <v>172.8226843274854</v>
+        <v>557.8226843274854</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,7 +8438,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>420.0430062450914</v>
+        <v>420.0430062450903</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -8447,16 +8447,16 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>544.2621276423173</v>
+        <v>929.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>862.2489580698366</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>455.2478695740938</v>
+        <v>439.6923140185369</v>
       </c>
       <c r="P8" t="n">
-        <v>369.7315044851222</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
         <v>172.8226843274854</v>
@@ -8675,7 +8675,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>128.4277587171436</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -8684,16 +8684,16 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N11" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>370.3619737970638</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8912,28 +8912,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>35.04300624509033</v>
+        <v>55.44822975121687</v>
       </c>
       <c r="K14" t="n">
         <v>559</v>
       </c>
       <c r="L14" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>163.6326220461452</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,28 +9149,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>35.04300624509033</v>
+        <v>55.44822975121687</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>559</v>
       </c>
-      <c r="L17" t="n">
-        <v>559.0000000000001</v>
-      </c>
       <c r="M17" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>93.67181251273416</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,25 +9389,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>801.385149773304</v>
+        <v>685.4145387153926</v>
       </c>
       <c r="N20" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O20" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,7 +9623,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -9638,13 +9638,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>90.65309308021877</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P23" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
-        <v>172.8226843274854</v>
+        <v>356.9661774925453</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,28 +9860,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>128.4277587171436</v>
+        <v>55.44822975121676</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L26" t="n">
         <v>559</v>
       </c>
       <c r="M26" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O26" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,28 +10097,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>477.2489580698352</v>
+        <v>661.3924512348951</v>
       </c>
       <c r="O29" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
         <v>559.2870600406815</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10343,7 +10343,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>801.385149773304</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
         <v>1036.248958069835</v>
@@ -10352,7 +10352,7 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
-        <v>559.2870600406815</v>
+        <v>300.4011642636528</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10577,22 +10577,22 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O35" t="n">
-        <v>211.4002806471676</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P35" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>172.8226843274854</v>
+        <v>356.9661774925453</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10814,10 +10814,10 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>536.4141414141418</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M38" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
         <v>1036.248958069835</v>
@@ -10826,10 +10826,10 @@
         <v>629.2478695740924</v>
       </c>
       <c r="P38" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,10 +11045,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>171.4188408091284</v>
       </c>
       <c r="K41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>777.3630622928066</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P41" t="n">
         <v>0.2870600406814136</v>
@@ -11288,22 +11288,22 @@
         <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O44" t="n">
-        <v>606.6620109882336</v>
+        <v>206.6237041381304</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q44" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.591170646055957</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -22715,7 +22715,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.59117064605573</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -22937,7 +22937,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.591170646055104</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.591170646055787</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.591170646055957</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.591170646055787</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -26269,10 +26269,10 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>1385272.737460797</v>
+      </c>
+      <c r="C2" t="n">
         <v>1385272.737460798</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1385272.737460797</v>
       </c>
       <c r="D2" t="n">
         <v>1385272.737460798</v>
@@ -26299,7 +26299,7 @@
         <v>1385314.744365854</v>
       </c>
       <c r="L2" t="n">
-        <v>1385314.744365853</v>
+        <v>1385314.744365854</v>
       </c>
       <c r="M2" t="n">
         <v>1385314.744365853</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540947.4312259532</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983395</v>
+        <v>533137.9258114472</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380802</v>
+        <v>531178.6502511877</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495091</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116067</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>621803.0125612888</v>
+        <v>620287.1568729725</v>
       </c>
       <c r="C6" t="n">
-        <v>759380.9926951026</v>
+        <v>757865.1370067875</v>
       </c>
       <c r="D6" t="n">
-        <v>761441.7646074194</v>
+        <v>759925.9089191031</v>
       </c>
       <c r="E6" t="n">
-        <v>437561.3411393185</v>
+        <v>435819.4913262109</v>
       </c>
       <c r="F6" t="n">
-        <v>780752.2364848229</v>
+        <v>779010.3866717151</v>
       </c>
       <c r="G6" t="n">
-        <v>782697.8129530082</v>
+        <v>780955.9631399006</v>
       </c>
       <c r="H6" t="n">
-        <v>784646.0897703097</v>
+        <v>782904.2399572023</v>
       </c>
       <c r="I6" t="n">
-        <v>786597.0864136697</v>
+        <v>784855.2366005623</v>
       </c>
       <c r="J6" t="n">
-        <v>373030.8226152946</v>
+        <v>371288.9728021867</v>
       </c>
       <c r="K6" t="n">
-        <v>790507.3183675143</v>
+        <v>788765.4685544065</v>
       </c>
       <c r="L6" t="n">
-        <v>792466.5939277731</v>
+        <v>790724.7441146662</v>
       </c>
       <c r="M6" t="n">
-        <v>733180.6698237526</v>
+        <v>731438.8200106451</v>
       </c>
       <c r="N6" t="n">
-        <v>796393.5668586063</v>
+        <v>794651.7170454983</v>
       </c>
       <c r="O6" t="n">
-        <v>518361.3061163449</v>
+        <v>516619.4563032371</v>
       </c>
       <c r="P6" t="n">
-        <v>800331.9089673546</v>
+        <v>798590.0591542468</v>
       </c>
     </row>
   </sheetData>
@@ -26993,7 +26993,7 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>350</v>
@@ -27005,7 +27005,7 @@
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N2" t="n">
         <v>-0</v>
@@ -27027,10 +27027,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -27042,13 +27042,13 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>-0</v>
@@ -27082,7 +27082,7 @@
         <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E4" t="n">
         <v>174</v>
@@ -27106,7 +27106,7 @@
         <v>-0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>174</v>
@@ -27451,10 +27451,10 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="I2" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27521,16 +27521,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>41.70910106771527</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>17.3083845693742</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27594,13 +27594,13 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D4" t="n">
+        <v>338.7529107212324</v>
+      </c>
+      <c r="E4" t="n">
         <v>400</v>
-      </c>
-      <c r="D4" t="n">
-        <v>400</v>
-      </c>
-      <c r="E4" t="n">
-        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
         <v>400</v>
@@ -27612,7 +27612,7 @@
         <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
         <v>400</v>
@@ -27645,7 +27645,7 @@
         <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
-        <v>251.3537162679223</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
         <v>150.9583912744579</v>
@@ -27660,7 +27660,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27721,7 +27721,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>371.2938086145853</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27736,7 +27736,7 @@
         <v>400</v>
       </c>
       <c r="X5" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="Y5" t="n">
         <v>400</v>
@@ -27752,13 +27752,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27800,16 +27800,16 @@
         <v>400</v>
       </c>
       <c r="S6" t="n">
+        <v>255.4358056469697</v>
+      </c>
+      <c r="T6" t="n">
         <v>400</v>
-      </c>
-      <c r="T6" t="n">
-        <v>251.3119749597991</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>400</v>
+        <v>29.51066719152016</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
@@ -27828,28 +27828,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
         <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
         <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
         <v>228.7711261016186</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J7" t="n">
         <v>35.26894883590776</v>
@@ -27879,10 +27879,10 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>246.6185464050333</v>
       </c>
       <c r="U7" t="n">
         <v>400</v>
@@ -27897,7 +27897,7 @@
         <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>367.0138648336894</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27922,13 +27922,13 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27986,7 +27986,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>282.1099053111968</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
@@ -27998,13 +27998,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>139.8182410159025</v>
       </c>
       <c r="G9" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>217.1263858913485</v>
@@ -28043,10 +28043,10 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>15.21035976018675</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>29.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
@@ -28065,10 +28065,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>348.6522536741804</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
         <v>400</v>
@@ -28077,13 +28077,13 @@
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
         <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T10" t="n">
+        <v>210.0245665062577</v>
+      </c>
+      <c r="U10" t="n">
+        <v>150.9583912744579</v>
+      </c>
+      <c r="V10" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W10" t="n">
+        <v>336.9137329713681</v>
+      </c>
+      <c r="X10" t="n">
         <v>400</v>
       </c>
-      <c r="T10" t="n">
+      <c r="Y10" t="n">
         <v>400</v>
-      </c>
-      <c r="U10" t="n">
-        <v>400</v>
-      </c>
-      <c r="V10" t="n">
-        <v>400</v>
-      </c>
-      <c r="W10" t="n">
-        <v>400</v>
-      </c>
-      <c r="X10" t="n">
-        <v>247.4436454301076</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28159,7 +28159,7 @@
         <v>350</v>
       </c>
       <c r="G11" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H11" t="n">
         <v>350</v>
@@ -28192,7 +28192,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S11" t="n">
         <v>350</v>
@@ -28223,13 +28223,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>350</v>
+        <v>154.448623365906</v>
       </c>
       <c r="C12" t="n">
         <v>350</v>
       </c>
       <c r="D12" t="n">
-        <v>108.3391894627398</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
         <v>342.6720972219126</v>
@@ -28244,7 +28244,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I12" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
         <v>350</v>
@@ -28399,7 +28399,7 @@
         <v>350</v>
       </c>
       <c r="H14" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I14" t="n">
         <v>150.0811596826846</v>
@@ -28441,7 +28441,7 @@
         <v>350</v>
       </c>
       <c r="V14" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="W14" t="n">
         <v>350</v>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>263.0617733495848</v>
+        <v>350</v>
       </c>
       <c r="C15" t="n">
         <v>350</v>
@@ -28475,7 +28475,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H15" t="n">
         <v>332.1680871864211</v>
@@ -28523,10 +28523,10 @@
         <v>350</v>
       </c>
       <c r="W15" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="Y15" t="n">
         <v>350</v>
@@ -28551,7 +28551,7 @@
         <v>350</v>
       </c>
       <c r="F16" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="G16" t="n">
         <v>350</v>
@@ -28593,7 +28593,7 @@
         <v>350</v>
       </c>
       <c r="T16" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U16" t="n">
         <v>350</v>
@@ -28630,7 +28630,7 @@
         <v>350</v>
       </c>
       <c r="F17" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="G17" t="n">
         <v>350</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S17" t="n">
         <v>350</v>
@@ -28709,16 +28709,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>252.6980156874616</v>
       </c>
       <c r="G18" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I18" t="n">
-        <v>136.6167105523271</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28867,7 +28867,7 @@
         <v>350</v>
       </c>
       <c r="F20" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="G20" t="n">
         <v>350</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S20" t="n">
         <v>350</v>
@@ -28940,13 +28940,13 @@
         <v>350</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>274.8961667101369</v>
       </c>
       <c r="E21" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>325.7395358750273</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>110.4015025650371</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
         <v>350</v>
@@ -28997,7 +28997,7 @@
         <v>350</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="X21" t="n">
         <v>350</v>
@@ -29076,10 +29076,10 @@
         <v>350</v>
       </c>
       <c r="W22" t="n">
+        <v>350</v>
+      </c>
+      <c r="X22" t="n">
         <v>342.2113306341341</v>
-      </c>
-      <c r="X22" t="n">
-        <v>350</v>
       </c>
       <c r="Y22" t="n">
         <v>350</v>
@@ -29092,7 +29092,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="C23" t="n">
         <v>350</v>
@@ -29155,7 +29155,7 @@
         <v>350</v>
       </c>
       <c r="W23" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="X23" t="n">
         <v>350</v>
@@ -29174,7 +29174,7 @@
         <v>350</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
@@ -29189,10 +29189,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H24" t="n">
-        <v>332.1680871864211</v>
+        <v>136.6167105523271</v>
       </c>
       <c r="I24" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -29237,7 +29237,7 @@
         <v>350</v>
       </c>
       <c r="X24" t="n">
-        <v>287.3222374745574</v>
+        <v>350</v>
       </c>
       <c r="Y24" t="n">
         <v>350</v>
@@ -29253,58 +29253,58 @@
         <v>350</v>
       </c>
       <c r="C25" t="n">
+        <v>350</v>
+      </c>
+      <c r="D25" t="n">
+        <v>350</v>
+      </c>
+      <c r="E25" t="n">
+        <v>350</v>
+      </c>
+      <c r="F25" t="n">
+        <v>350</v>
+      </c>
+      <c r="G25" t="n">
+        <v>350</v>
+      </c>
+      <c r="H25" t="n">
+        <v>350</v>
+      </c>
+      <c r="I25" t="n">
+        <v>350</v>
+      </c>
+      <c r="J25" t="n">
+        <v>350</v>
+      </c>
+      <c r="K25" t="n">
+        <v>350</v>
+      </c>
+      <c r="L25" t="n">
+        <v>350</v>
+      </c>
+      <c r="M25" t="n">
+        <v>350</v>
+      </c>
+      <c r="N25" t="n">
+        <v>350</v>
+      </c>
+      <c r="O25" t="n">
+        <v>350</v>
+      </c>
+      <c r="P25" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>350</v>
+      </c>
+      <c r="R25" t="n">
+        <v>350</v>
+      </c>
+      <c r="S25" t="n">
+        <v>350</v>
+      </c>
+      <c r="T25" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="D25" t="n">
-        <v>350</v>
-      </c>
-      <c r="E25" t="n">
-        <v>350</v>
-      </c>
-      <c r="F25" t="n">
-        <v>350</v>
-      </c>
-      <c r="G25" t="n">
-        <v>350</v>
-      </c>
-      <c r="H25" t="n">
-        <v>350</v>
-      </c>
-      <c r="I25" t="n">
-        <v>350</v>
-      </c>
-      <c r="J25" t="n">
-        <v>350</v>
-      </c>
-      <c r="K25" t="n">
-        <v>350</v>
-      </c>
-      <c r="L25" t="n">
-        <v>350</v>
-      </c>
-      <c r="M25" t="n">
-        <v>350</v>
-      </c>
-      <c r="N25" t="n">
-        <v>350</v>
-      </c>
-      <c r="O25" t="n">
-        <v>350</v>
-      </c>
-      <c r="P25" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>350</v>
-      </c>
-      <c r="R25" t="n">
-        <v>350</v>
-      </c>
-      <c r="S25" t="n">
-        <v>350</v>
-      </c>
-      <c r="T25" t="n">
-        <v>350</v>
       </c>
       <c r="U25" t="n">
         <v>350</v>
@@ -29344,7 +29344,7 @@
         <v>350</v>
       </c>
       <c r="G26" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H26" t="n">
         <v>350</v>
@@ -29380,7 +29380,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S26" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T26" t="n">
         <v>350</v>
@@ -29411,13 +29411,13 @@
         <v>350</v>
       </c>
       <c r="C27" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>279.9943346964702</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
         <v>339.6362423378769</v>
@@ -29456,10 +29456,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R27" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="T27" t="n">
         <v>350</v>
@@ -29584,7 +29584,7 @@
         <v>350</v>
       </c>
       <c r="H29" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I29" t="n">
         <v>150.0811596826846</v>
@@ -29623,7 +29623,7 @@
         <v>350</v>
       </c>
       <c r="U29" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="V29" t="n">
         <v>350</v>
@@ -29645,7 +29645,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>350</v>
@@ -29660,10 +29660,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>325.7395358750273</v>
+        <v>263.0617733495848</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I30" t="n">
         <v>217.1263858913485</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>92.56958975145824</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
         <v>350</v>
@@ -29854,7 +29854,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S32" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T32" t="n">
         <v>350</v>
@@ -29866,7 +29866,7 @@
         <v>350</v>
       </c>
       <c r="W32" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="X32" t="n">
         <v>350</v>
@@ -29891,7 +29891,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>262.1624218828912</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
         <v>339.6362423378769</v>
@@ -29900,10 +29900,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>136.6167105523271</v>
       </c>
       <c r="I33" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29973,7 +29973,7 @@
         <v>350</v>
       </c>
       <c r="F34" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="G34" t="n">
         <v>350</v>
@@ -30015,7 +30015,7 @@
         <v>350</v>
       </c>
       <c r="T34" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U34" t="n">
         <v>350</v>
@@ -30088,10 +30088,10 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S35" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T35" t="n">
         <v>350</v>
@@ -30122,13 +30122,13 @@
         <v>350</v>
       </c>
       <c r="C36" t="n">
-        <v>276.9584798124343</v>
+        <v>350</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>269.6305770343469</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -30210,7 +30210,7 @@
         <v>350</v>
       </c>
       <c r="F37" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="G37" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S38" t="n">
         <v>350</v>
@@ -30340,7 +30340,7 @@
         <v>350</v>
       </c>
       <c r="W38" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="X38" t="n">
         <v>350</v>
@@ -30371,10 +30371,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>325.7395358750273</v>
+        <v>245.2298605360059</v>
       </c>
       <c r="H39" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>217.1263858913485</v>
@@ -30404,7 +30404,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S39" t="n">
         <v>350</v>
@@ -30416,7 +30416,7 @@
         <v>350</v>
       </c>
       <c r="V39" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="W39" t="n">
         <v>350</v>
@@ -30441,55 +30441,55 @@
         <v>350</v>
       </c>
       <c r="D40" t="n">
+        <v>350</v>
+      </c>
+      <c r="E40" t="n">
+        <v>350</v>
+      </c>
+      <c r="F40" t="n">
+        <v>350</v>
+      </c>
+      <c r="G40" t="n">
+        <v>350</v>
+      </c>
+      <c r="H40" t="n">
+        <v>350</v>
+      </c>
+      <c r="I40" t="n">
+        <v>350</v>
+      </c>
+      <c r="J40" t="n">
+        <v>350</v>
+      </c>
+      <c r="K40" t="n">
+        <v>350</v>
+      </c>
+      <c r="L40" t="n">
+        <v>350</v>
+      </c>
+      <c r="M40" t="n">
+        <v>350</v>
+      </c>
+      <c r="N40" t="n">
+        <v>350</v>
+      </c>
+      <c r="O40" t="n">
+        <v>350</v>
+      </c>
+      <c r="P40" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>350</v>
+      </c>
+      <c r="R40" t="n">
+        <v>350</v>
+      </c>
+      <c r="S40" t="n">
+        <v>350</v>
+      </c>
+      <c r="T40" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="E40" t="n">
-        <v>350</v>
-      </c>
-      <c r="F40" t="n">
-        <v>350</v>
-      </c>
-      <c r="G40" t="n">
-        <v>350</v>
-      </c>
-      <c r="H40" t="n">
-        <v>350</v>
-      </c>
-      <c r="I40" t="n">
-        <v>350</v>
-      </c>
-      <c r="J40" t="n">
-        <v>350</v>
-      </c>
-      <c r="K40" t="n">
-        <v>350</v>
-      </c>
-      <c r="L40" t="n">
-        <v>350</v>
-      </c>
-      <c r="M40" t="n">
-        <v>350</v>
-      </c>
-      <c r="N40" t="n">
-        <v>350</v>
-      </c>
-      <c r="O40" t="n">
-        <v>350</v>
-      </c>
-      <c r="P40" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>350</v>
-      </c>
-      <c r="R40" t="n">
-        <v>350</v>
-      </c>
-      <c r="S40" t="n">
-        <v>350</v>
-      </c>
-      <c r="T40" t="n">
-        <v>350</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30535,7 +30535,7 @@
         <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S41" t="n">
         <v>350</v>
@@ -30593,7 +30593,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="C42" t="n">
         <v>350</v>
@@ -30641,7 +30641,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>350</v>
@@ -30656,10 +30656,10 @@
         <v>350</v>
       </c>
       <c r="W42" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Y42" t="n">
         <v>350</v>
@@ -30760,7 +30760,7 @@
         <v>350</v>
       </c>
       <c r="E44" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="F44" t="n">
         <v>350</v>
@@ -30817,7 +30817,7 @@
         <v>350</v>
       </c>
       <c r="X44" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="Y44" t="n">
         <v>350</v>
@@ -30848,7 +30848,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I45" t="n">
         <v>217.1263858913485</v>
@@ -30875,10 +30875,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>92.56958975145824</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>350</v>
@@ -30899,7 +30899,7 @@
         <v>350</v>
       </c>
       <c r="Y45" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
     </row>
     <row r="46">
@@ -30936,34 +30936,34 @@
         <v>350</v>
       </c>
       <c r="K46" t="n">
+        <v>350</v>
+      </c>
+      <c r="L46" t="n">
+        <v>350</v>
+      </c>
+      <c r="M46" t="n">
+        <v>350</v>
+      </c>
+      <c r="N46" t="n">
+        <v>350</v>
+      </c>
+      <c r="O46" t="n">
+        <v>350</v>
+      </c>
+      <c r="P46" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>350</v>
+      </c>
+      <c r="R46" t="n">
+        <v>350</v>
+      </c>
+      <c r="S46" t="n">
+        <v>350</v>
+      </c>
+      <c r="T46" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="L46" t="n">
-        <v>350</v>
-      </c>
-      <c r="M46" t="n">
-        <v>350</v>
-      </c>
-      <c r="N46" t="n">
-        <v>350</v>
-      </c>
-      <c r="O46" t="n">
-        <v>350</v>
-      </c>
-      <c r="P46" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>350</v>
-      </c>
-      <c r="R46" t="n">
-        <v>350</v>
-      </c>
-      <c r="S46" t="n">
-        <v>350</v>
-      </c>
-      <c r="T46" t="n">
-        <v>350</v>
       </c>
       <c r="U46" t="n">
         <v>350</v>
@@ -34743,7 +34743,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -34758,13 +34758,13 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>369.4444444444443</v>
+        <v>385</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="Q2" t="n">
-        <v>385</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34880,13 +34880,13 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>53.21669266567693</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
         <v>125.6171440322581</v>
@@ -34898,7 +34898,7 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
         <v>364.7310511640923</v>
@@ -34931,7 +34931,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>41.32914976166459</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -34946,7 +34946,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,7 +34980,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -34992,16 +34992,16 @@
         <v>385</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>369.4444444444444</v>
+      </c>
+      <c r="P5" t="n">
         <v>385</v>
       </c>
-      <c r="O5" t="n">
-        <v>369.4444444444445</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,28 +35114,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -35165,10 +35165,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>36.59397989877561</v>
       </c>
       <c r="U7" t="n">
         <v>249.0416087255421</v>
@@ -35183,7 +35183,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>79.54851198422703</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35217,7 +35217,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>385.0000000000011</v>
+        <v>385</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -35226,16 +35226,16 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="N8" t="n">
-        <v>385.0000000000014</v>
+        <v>385</v>
       </c>
       <c r="O8" t="n">
-        <v>385.0000000000014</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="P8" t="n">
-        <v>369.4444444444408</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35351,10 +35351,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61.53845333710178</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
         <v>114.4637819444445</v>
@@ -35363,13 +35363,13 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
         <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
         <v>223.3665443798817</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>110.5409231326584</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35454,7 +35454,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>395.2617303410664</v>
+        <v>93.38475247205324</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -35463,16 +35463,16 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>559</v>
       </c>
       <c r="O11" t="n">
-        <v>300.1141042229714</v>
+        <v>559</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q11" t="n">
         <v>443.0293889420883</v>
@@ -35691,28 +35691,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>20.40522350612654</v>
       </c>
       <c r="K14" t="n">
         <v>559</v>
       </c>
       <c r="L14" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
         <v>559</v>
       </c>
       <c r="O14" t="n">
-        <v>93.38475247205275</v>
+        <v>559</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35837,7 +35837,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F16" t="n">
-        <v>67.82847466639221</v>
+        <v>75.61714403225807</v>
       </c>
       <c r="G16" t="n">
         <v>104.95612715847</v>
@@ -35879,7 +35879,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U16" t="n">
         <v>199.0416087255421</v>
@@ -35928,28 +35928,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>20.40522350612654</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>559</v>
       </c>
-      <c r="L17" t="n">
-        <v>559.0000000000001</v>
-      </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
         <v>559</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P17" t="n">
-        <v>93.38475247205275</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36168,25 +36168,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>257.1230221309867</v>
+        <v>141.1524110730753</v>
       </c>
       <c r="N20" t="n">
         <v>559</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36362,10 +36362,10 @@
         <v>150.8296897837838</v>
       </c>
       <c r="W22" t="n">
-        <v>115.8385207954244</v>
+        <v>123.6271901612903</v>
       </c>
       <c r="X22" t="n">
-        <v>102.5563545698924</v>
+        <v>94.76768520402656</v>
       </c>
       <c r="Y22" t="n">
         <v>62.53464715053764</v>
@@ -36402,7 +36402,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -36417,13 +36417,13 @@
         <v>559</v>
       </c>
       <c r="O23" t="n">
-        <v>20.40522350612631</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36539,7 +36539,7 @@
         <v>62.88619966292134</v>
       </c>
       <c r="C25" t="n">
-        <v>69.48608398608951</v>
+        <v>77.27475335195533</v>
       </c>
       <c r="D25" t="n">
         <v>64.46378194444452</v>
@@ -36590,7 +36590,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U25" t="n">
         <v>199.0416087255421</v>
@@ -36639,28 +36639,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>93.38475247205329</v>
+        <v>20.40522350612643</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L26" t="n">
         <v>559</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O26" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36876,28 +36876,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="O29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>559</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37122,7 +37122,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>257.1230221309867</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
         <v>559</v>
@@ -37131,7 +37131,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>559</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="Q32" t="n">
         <v>443.0293889420883</v>
@@ -37259,7 +37259,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F34" t="n">
-        <v>67.82847466639221</v>
+        <v>75.61714403225807</v>
       </c>
       <c r="G34" t="n">
         <v>104.95612715847</v>
@@ -37301,7 +37301,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U34" t="n">
         <v>199.0416087255421</v>
@@ -37356,22 +37356,22 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
         <v>559</v>
       </c>
       <c r="O35" t="n">
-        <v>141.1524110730751</v>
+        <v>559</v>
       </c>
       <c r="P35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37496,7 +37496,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F37" t="n">
-        <v>67.82847466639221</v>
+        <v>75.61714403225807</v>
       </c>
       <c r="G37" t="n">
         <v>104.95612715847</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37593,10 +37593,10 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>536.4141414141418</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
         <v>559</v>
@@ -37605,10 +37605,10 @@
         <v>559</v>
       </c>
       <c r="P38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37727,7 +37727,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D40" t="n">
-        <v>56.67511257857869</v>
+        <v>64.46378194444452</v>
       </c>
       <c r="E40" t="n">
         <v>69.01909516304346</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37824,10 +37824,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>395.2617303410664</v>
+        <v>136.375834564038</v>
       </c>
       <c r="K41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -37836,10 +37836,10 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>300.1141042229714</v>
+        <v>559</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -38067,22 +38067,22 @@
         <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>136.375834564038</v>
+      </c>
+      <c r="P44" t="n">
         <v>559</v>
       </c>
-      <c r="O44" t="n">
-        <v>536.4141414141411</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38222,7 +38222,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K46" t="n">
-        <v>53.69055683299113</v>
+        <v>61.47922619885696</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U46" t="n">
         <v>199.0416087255421</v>
